--- a/EffidermaDocs/Share Folder/Top15 Active Database.xlsx
+++ b/EffidermaDocs/Share Folder/Top15 Active Database.xlsx
@@ -1371,14 +1371,14 @@
     <t>Image</t>
   </si>
   <si>
-    <t>One number from Efficacy data</t>
+    <t>Grams per 100g total active + base</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1409,6 +1409,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Carlito"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1459,7 +1472,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1496,6 +1509,12 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2478,7 +2497,7 @@
       <c r="AB1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" s="7" t="s">
+      <c r="AC1" s="17" t="s">
         <v>440</v>
       </c>
       <c r="AD1" s="7" t="s">
@@ -2612,6 +2631,9 @@
       <c r="AB2" t="s">
         <v>67</v>
       </c>
+      <c r="AC2" s="18">
+        <v>2</v>
+      </c>
       <c r="AD2" t="s">
         <v>310</v>
       </c>
@@ -2737,6 +2759,9 @@
       <c r="AB3" t="s">
         <v>328</v>
       </c>
+      <c r="AC3" s="18">
+        <v>2</v>
+      </c>
       <c r="AD3" t="s">
         <v>349</v>
       </c>
@@ -2865,6 +2890,9 @@
       <c r="AB4" t="s">
         <v>305</v>
       </c>
+      <c r="AC4" s="18">
+        <v>3</v>
+      </c>
       <c r="AD4" t="s">
         <v>349</v>
       </c>
@@ -2993,6 +3021,9 @@
       <c r="AB5" t="s">
         <v>80</v>
       </c>
+      <c r="AC5" s="18">
+        <v>2</v>
+      </c>
       <c r="AD5" t="s">
         <v>349</v>
       </c>
@@ -3118,6 +3149,9 @@
       <c r="AB6" t="s">
         <v>163</v>
       </c>
+      <c r="AC6" s="18">
+        <v>2</v>
+      </c>
       <c r="AD6" t="s">
         <v>349</v>
       </c>
@@ -3243,6 +3277,9 @@
       <c r="AB7" t="s">
         <v>297</v>
       </c>
+      <c r="AC7" s="18">
+        <v>2</v>
+      </c>
       <c r="AD7" t="s">
         <v>298</v>
       </c>
@@ -3371,6 +3408,9 @@
       <c r="AB8" t="s">
         <v>341</v>
       </c>
+      <c r="AC8" s="18">
+        <v>1</v>
+      </c>
       <c r="AD8" t="s">
         <v>91</v>
       </c>
@@ -3496,6 +3536,9 @@
       <c r="AB9" t="s">
         <v>340</v>
       </c>
+      <c r="AC9" s="18">
+        <v>1.5</v>
+      </c>
       <c r="AD9" t="s">
         <v>102</v>
       </c>
@@ -3621,7 +3664,9 @@
       <c r="AB10" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="AC10" s="4"/>
+      <c r="AC10" s="18">
+        <v>0.5</v>
+      </c>
       <c r="AD10" t="s">
         <v>349</v>
       </c>
@@ -3744,6 +3789,9 @@
       <c r="AB11" t="s">
         <v>315</v>
       </c>
+      <c r="AC11" s="18">
+        <v>2</v>
+      </c>
       <c r="AD11" t="s">
         <v>317</v>
       </c>
@@ -3872,6 +3920,9 @@
       <c r="AB12" t="s">
         <v>113</v>
       </c>
+      <c r="AC12" s="18">
+        <v>1</v>
+      </c>
       <c r="AD12" t="s">
         <v>331</v>
       </c>
@@ -4003,6 +4054,9 @@
       <c r="AB13" t="s">
         <v>122</v>
       </c>
+      <c r="AC13" s="18">
+        <v>2</v>
+      </c>
       <c r="AD13" t="s">
         <v>349</v>
       </c>
@@ -4128,6 +4182,9 @@
       <c r="AB14" t="s">
         <v>53</v>
       </c>
+      <c r="AC14" s="18">
+        <v>2</v>
+      </c>
       <c r="AD14" t="s">
         <v>54</v>
       </c>
@@ -4253,6 +4310,9 @@
       <c r="AB15" t="s">
         <v>321</v>
       </c>
+      <c r="AC15" s="18">
+        <v>1</v>
+      </c>
       <c r="AD15" t="s">
         <v>349</v>
       </c>
@@ -4377,6 +4437,9 @@
       </c>
       <c r="AB16" t="s">
         <v>336</v>
+      </c>
+      <c r="AC16" s="18">
+        <v>2</v>
       </c>
       <c r="AD16" t="s">
         <v>338</v>
@@ -5610,10 +5673,10 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="34.9375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="7.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.0625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="67.3125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="43.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.4375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.25" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="8.75" style="2"/>
   </cols>
   <sheetData>
@@ -5622,13 +5685,13 @@
         <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>429</v>
@@ -5638,12 +5701,12 @@
       <c r="A2" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16" t="s">
+      <c r="B2" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16" t="s">
         <v>439</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>427</v>
@@ -5653,11 +5716,11 @@
       <c r="A3" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>208</v>
+      </c>
       <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
-        <v>208</v>
-      </c>
+      <c r="D3" s="3"/>
       <c r="E3" s="2" t="s">
         <v>428</v>
       </c>
@@ -5666,11 +5729,11 @@
       <c r="A4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>209</v>
+      </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="3" t="s">
-        <v>209</v>
-      </c>
+      <c r="D4" s="3"/>
       <c r="E4" s="2" t="s">
         <v>430</v>
       </c>
@@ -5679,11 +5742,11 @@
       <c r="A5" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="B5" s="16"/>
+      <c r="B5" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="C5" s="16"/>
-      <c r="D5" s="3" t="s">
-        <v>210</v>
-      </c>
+      <c r="D5" s="16"/>
       <c r="E5" s="2" t="s">
         <v>432</v>
       </c>
@@ -5692,11 +5755,11 @@
       <c r="A6" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>212</v>
+      </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="3" t="s">
-        <v>212</v>
-      </c>
+      <c r="D6" s="3"/>
       <c r="E6" s="2" t="s">
         <v>433</v>
       </c>
@@ -5705,11 +5768,11 @@
       <c r="A7" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="3"/>
+      <c r="B7" s="3" t="s">
+        <v>213</v>
+      </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="3" t="s">
-        <v>213</v>
-      </c>
+      <c r="D7" s="3"/>
       <c r="E7" s="2" t="s">
         <v>434</v>
       </c>
@@ -5718,87 +5781,87 @@
       <c r="A8" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3" t="s">
+      <c r="B8" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="27">
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3" t="s">
+      <c r="B9" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3" t="s">
         <v>438</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>216</v>
+      </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="3" t="s">
-        <v>216</v>
-      </c>
+      <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="B11" s="16"/>
+      <c r="B11" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="C11" s="16"/>
-      <c r="D11" s="3" t="s">
-        <v>217</v>
-      </c>
+      <c r="D11" s="16"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3" t="s">
+      <c r="B12" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3" t="s">
         <v>436</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>220</v>
+      </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="3" t="s">
-        <v>220</v>
-      </c>
+      <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>221</v>
+      </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="3" t="s">
-        <v>221</v>
-      </c>
+      <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>222</v>
+      </c>
       <c r="C15" s="3"/>
-      <c r="D15" s="3" t="s">
-        <v>222</v>
-      </c>
+      <c r="D15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5806,12 +5869,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c8e02472-428d-4e4b-a8a2-4a2d4b78b5a4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2a9cfe5d-ebc6-4618-adda-f78230cc5c80" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6056,20 +6121,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c8e02472-428d-4e4b-a8a2-4a2d4b78b5a4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2a9cfe5d-ebc6-4618-adda-f78230cc5c80" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C4E8E74-0ACF-462B-8592-1E85EB24E49A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6D184B-1DEC-4814-A960-29639CBF9650}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c8e02472-428d-4e4b-a8a2-4a2d4b78b5a4"/>
+    <ds:schemaRef ds:uri="2a9cfe5d-ebc6-4618-adda-f78230cc5c80"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6094,12 +6160,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6D184B-1DEC-4814-A960-29639CBF9650}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C4E8E74-0ACF-462B-8592-1E85EB24E49A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c8e02472-428d-4e4b-a8a2-4a2d4b78b5a4"/>
-    <ds:schemaRef ds:uri="2a9cfe5d-ebc6-4618-adda-f78230cc5c80"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/EffidermaDocs/Share Folder/Top15 Active Database.xlsx
+++ b/EffidermaDocs/Share Folder/Top15 Active Database.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-16320" windowWidth="29040" windowHeight="15840" activeTab="2"/>
+    <workbookView xWindow="28680" yWindow="-16320" windowWidth="29040" windowHeight="15840" firstSheet="5" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Actives" sheetId="6" r:id="rId1"/>
@@ -18,6 +18,8 @@
     <sheet name="Compatibility" sheetId="8" r:id="rId4"/>
     <sheet name="Scoring Guide" sheetId="4" r:id="rId5"/>
     <sheet name="AI Taxonomy" sheetId="3" r:id="rId6"/>
+    <sheet name="anodiam_skin_concern_detection" sheetId="9" r:id="rId7"/>
+    <sheet name="anodiam_user_skin_concern_score" sheetId="10" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Bases!$A$1:$N$6</definedName>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="507">
   <si>
     <t>Ingredient</t>
   </si>
@@ -1372,13 +1374,211 @@
   </si>
   <si>
     <t>Grams per 100g total active + base</t>
+  </si>
+  <si>
+    <t>skin_concern_id</t>
+  </si>
+  <si>
+    <t>skin_concern_name</t>
+  </si>
+  <si>
+    <t>Dry Skin</t>
+  </si>
+  <si>
+    <t>Dehydrated Skin</t>
+  </si>
+  <si>
+    <t>Compromised Skin Barrier</t>
+  </si>
+  <si>
+    <t>Redness</t>
+  </si>
+  <si>
+    <t>Itching / Irritation</t>
+  </si>
+  <si>
+    <t>Reactive Skin</t>
+  </si>
+  <si>
+    <t>Acne</t>
+  </si>
+  <si>
+    <t>Breakouts / Blemishes</t>
+  </si>
+  <si>
+    <t>Excess Sebum (Oily Skin)</t>
+  </si>
+  <si>
+    <t>Enlarged Pores</t>
+  </si>
+  <si>
+    <t>Blackheads / Comedones</t>
+  </si>
+  <si>
+    <t>Fine Lines</t>
+  </si>
+  <si>
+    <t>Wrinkles</t>
+  </si>
+  <si>
+    <t>Expression Lines</t>
+  </si>
+  <si>
+    <t>Loss of Firmness</t>
+  </si>
+  <si>
+    <t>Mature Skin</t>
+  </si>
+  <si>
+    <t>Uneven Skin Tone</t>
+  </si>
+  <si>
+    <t>Hyperpigmentation</t>
+  </si>
+  <si>
+    <t>Age Spots</t>
+  </si>
+  <si>
+    <t>Melasma-like Pigmentation</t>
+  </si>
+  <si>
+    <t>Dullness / Poor Radiance</t>
+  </si>
+  <si>
+    <t>Fatigued Skin</t>
+  </si>
+  <si>
+    <t>Photoaging</t>
+  </si>
+  <si>
+    <t>Environmental Skin Stress</t>
+  </si>
+  <si>
+    <t>Blue Light Exposure Risk</t>
+  </si>
+  <si>
+    <t>Microbiome Imbalance Risk</t>
+  </si>
+  <si>
+    <t>Chronic Skin Inflammation Risk</t>
+  </si>
+  <si>
+    <t>Skin Ageing / Longevity Risk</t>
+  </si>
+  <si>
+    <t>Stretch Marks</t>
+  </si>
+  <si>
+    <t>Scar / Repair Needs</t>
+  </si>
+  <si>
+    <t>detectable_by_questionnaire</t>
+  </si>
+  <si>
+    <t>detectable_by_selfie</t>
+  </si>
+  <si>
+    <t>SC0001</t>
+  </si>
+  <si>
+    <t>SC0002</t>
+  </si>
+  <si>
+    <t>SC0003</t>
+  </si>
+  <si>
+    <t>SC0004</t>
+  </si>
+  <si>
+    <t>SC0005</t>
+  </si>
+  <si>
+    <t>SC0006</t>
+  </si>
+  <si>
+    <t>SC0007</t>
+  </si>
+  <si>
+    <t>SC0008</t>
+  </si>
+  <si>
+    <t>SC0009</t>
+  </si>
+  <si>
+    <t>SC0010</t>
+  </si>
+  <si>
+    <t>SC0011</t>
+  </si>
+  <si>
+    <t>SC0012</t>
+  </si>
+  <si>
+    <t>SC0013</t>
+  </si>
+  <si>
+    <t>SC0014</t>
+  </si>
+  <si>
+    <t>SC0015</t>
+  </si>
+  <si>
+    <t>SC0016</t>
+  </si>
+  <si>
+    <t>SC0017</t>
+  </si>
+  <si>
+    <t>SC0018</t>
+  </si>
+  <si>
+    <t>SC0019</t>
+  </si>
+  <si>
+    <t>SC1001</t>
+  </si>
+  <si>
+    <t>SC1002</t>
+  </si>
+  <si>
+    <t>SC1003</t>
+  </si>
+  <si>
+    <t>SC1004</t>
+  </si>
+  <si>
+    <t>SC1005</t>
+  </si>
+  <si>
+    <t>SC1006</t>
+  </si>
+  <si>
+    <t>SC1007</t>
+  </si>
+  <si>
+    <t>SC1008</t>
+  </si>
+  <si>
+    <t>SC1009</t>
+  </si>
+  <si>
+    <t>SC2001</t>
+  </si>
+  <si>
+    <t>SC2002</t>
+  </si>
+  <si>
+    <t>SC2003</t>
+  </si>
+  <si>
+    <t>SC2004</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1413,6 +1613,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1472,7 +1680,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1510,11 +1718,23 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5868,6 +6088,962 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr defaultColWidth="56.1875" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="15.0625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="13.9">
+      <c r="A1" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>474</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="19" t="s">
+        <v>475</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>443</v>
+      </c>
+      <c r="C2" s="22">
+        <v>1</v>
+      </c>
+      <c r="D2" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="19" t="s">
+        <v>476</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>444</v>
+      </c>
+      <c r="C3" s="22">
+        <v>1</v>
+      </c>
+      <c r="D3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="19" t="s">
+        <v>477</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>445</v>
+      </c>
+      <c r="C4" s="22">
+        <v>1</v>
+      </c>
+      <c r="D4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="C5" s="22">
+        <v>1</v>
+      </c>
+      <c r="D5" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="19" t="s">
+        <v>479</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>446</v>
+      </c>
+      <c r="C6" s="22">
+        <v>1</v>
+      </c>
+      <c r="D6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="19" t="s">
+        <v>480</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="C7" s="22">
+        <v>1</v>
+      </c>
+      <c r="D7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="19" t="s">
+        <v>481</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>448</v>
+      </c>
+      <c r="C8" s="22">
+        <v>1</v>
+      </c>
+      <c r="D8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="19" t="s">
+        <v>482</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>449</v>
+      </c>
+      <c r="C9" s="22">
+        <v>1</v>
+      </c>
+      <c r="D9" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="19" t="s">
+        <v>483</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>450</v>
+      </c>
+      <c r="C10" s="22">
+        <v>1</v>
+      </c>
+      <c r="D10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="19" t="s">
+        <v>484</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>451</v>
+      </c>
+      <c r="C11" s="22">
+        <v>1</v>
+      </c>
+      <c r="D11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="19" t="s">
+        <v>485</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>458</v>
+      </c>
+      <c r="C12" s="22">
+        <v>1</v>
+      </c>
+      <c r="D12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="19" t="s">
+        <v>486</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>459</v>
+      </c>
+      <c r="C13" s="22">
+        <v>1</v>
+      </c>
+      <c r="D13" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>460</v>
+      </c>
+      <c r="C14" s="22">
+        <v>1</v>
+      </c>
+      <c r="D14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="19" t="s">
+        <v>488</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>462</v>
+      </c>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="19" t="s">
+        <v>489</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>463</v>
+      </c>
+      <c r="C16" s="22">
+        <v>1</v>
+      </c>
+      <c r="D16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="19" t="s">
+        <v>490</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>464</v>
+      </c>
+      <c r="C17" s="22">
+        <v>1</v>
+      </c>
+      <c r="D17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="19" t="s">
+        <v>491</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>465</v>
+      </c>
+      <c r="C18" s="22">
+        <v>1</v>
+      </c>
+      <c r="D18" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>469</v>
+      </c>
+      <c r="C19" s="22">
+        <v>1</v>
+      </c>
+      <c r="D19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="19" t="s">
+        <v>493</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>470</v>
+      </c>
+      <c r="C20" s="22">
+        <v>1</v>
+      </c>
+      <c r="D20" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="19" t="s">
+        <v>494</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>452</v>
+      </c>
+      <c r="C21" s="22">
+        <v>1</v>
+      </c>
+      <c r="D21" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="19" t="s">
+        <v>495</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>453</v>
+      </c>
+      <c r="C22" s="22">
+        <v>1</v>
+      </c>
+      <c r="D22" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="19" t="s">
+        <v>496</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>454</v>
+      </c>
+      <c r="C23" s="22">
+        <v>1</v>
+      </c>
+      <c r="D23" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="19" t="s">
+        <v>497</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>455</v>
+      </c>
+      <c r="C24" s="22">
+        <v>1</v>
+      </c>
+      <c r="D24" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>456</v>
+      </c>
+      <c r="C25" s="22">
+        <v>1</v>
+      </c>
+      <c r="D25" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="19" t="s">
+        <v>499</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>457</v>
+      </c>
+      <c r="C26" s="22">
+        <v>1</v>
+      </c>
+      <c r="D26" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>461</v>
+      </c>
+      <c r="C27" s="22">
+        <v>1</v>
+      </c>
+      <c r="D27" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>471</v>
+      </c>
+      <c r="C28" s="22">
+        <v>1</v>
+      </c>
+      <c r="D28" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>472</v>
+      </c>
+      <c r="C29" s="22">
+        <v>1</v>
+      </c>
+      <c r="D29" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="19" t="s">
+        <v>503</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>447</v>
+      </c>
+      <c r="C30" s="22">
+        <v>0</v>
+      </c>
+      <c r="D30" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>466</v>
+      </c>
+      <c r="C31" s="22">
+        <v>0</v>
+      </c>
+      <c r="D31" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>467</v>
+      </c>
+      <c r="C32" s="22">
+        <v>0</v>
+      </c>
+      <c r="D32" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>468</v>
+      </c>
+      <c r="C33" s="22">
+        <v>0</v>
+      </c>
+      <c r="D33" s="22">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr defaultColWidth="56.1875" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="15.0625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="13.9">
+      <c r="A1" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>474</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="19" t="s">
+        <v>475</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>443</v>
+      </c>
+      <c r="C2" s="22">
+        <v>1</v>
+      </c>
+      <c r="D2" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="19" t="s">
+        <v>476</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>444</v>
+      </c>
+      <c r="C3" s="22">
+        <v>1</v>
+      </c>
+      <c r="D3" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="19" t="s">
+        <v>477</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>445</v>
+      </c>
+      <c r="C4" s="22">
+        <v>1</v>
+      </c>
+      <c r="D4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="C5" s="22">
+        <v>1</v>
+      </c>
+      <c r="D5" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="19" t="s">
+        <v>479</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>446</v>
+      </c>
+      <c r="C6" s="22">
+        <v>1</v>
+      </c>
+      <c r="D6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="19" t="s">
+        <v>480</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="C7" s="22">
+        <v>1</v>
+      </c>
+      <c r="D7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="19" t="s">
+        <v>481</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>448</v>
+      </c>
+      <c r="C8" s="22">
+        <v>1</v>
+      </c>
+      <c r="D8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="19" t="s">
+        <v>482</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>449</v>
+      </c>
+      <c r="C9" s="22">
+        <v>1</v>
+      </c>
+      <c r="D9" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="19" t="s">
+        <v>483</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>450</v>
+      </c>
+      <c r="C10" s="22">
+        <v>1</v>
+      </c>
+      <c r="D10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="19" t="s">
+        <v>484</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>451</v>
+      </c>
+      <c r="C11" s="22">
+        <v>1</v>
+      </c>
+      <c r="D11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="19" t="s">
+        <v>485</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>458</v>
+      </c>
+      <c r="C12" s="22">
+        <v>1</v>
+      </c>
+      <c r="D12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="19" t="s">
+        <v>486</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>459</v>
+      </c>
+      <c r="C13" s="22">
+        <v>1</v>
+      </c>
+      <c r="D13" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>460</v>
+      </c>
+      <c r="C14" s="22">
+        <v>1</v>
+      </c>
+      <c r="D14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="19" t="s">
+        <v>488</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>462</v>
+      </c>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="19" t="s">
+        <v>489</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>463</v>
+      </c>
+      <c r="C16" s="22">
+        <v>1</v>
+      </c>
+      <c r="D16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="19" t="s">
+        <v>490</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>464</v>
+      </c>
+      <c r="C17" s="22">
+        <v>1</v>
+      </c>
+      <c r="D17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="19" t="s">
+        <v>491</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>465</v>
+      </c>
+      <c r="C18" s="22">
+        <v>1</v>
+      </c>
+      <c r="D18" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>469</v>
+      </c>
+      <c r="C19" s="22">
+        <v>1</v>
+      </c>
+      <c r="D19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="19" t="s">
+        <v>493</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>470</v>
+      </c>
+      <c r="C20" s="22">
+        <v>1</v>
+      </c>
+      <c r="D20" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="19" t="s">
+        <v>494</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>452</v>
+      </c>
+      <c r="C21" s="22">
+        <v>1</v>
+      </c>
+      <c r="D21" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="19" t="s">
+        <v>495</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>453</v>
+      </c>
+      <c r="C22" s="22">
+        <v>1</v>
+      </c>
+      <c r="D22" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="19" t="s">
+        <v>496</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>454</v>
+      </c>
+      <c r="C23" s="22">
+        <v>1</v>
+      </c>
+      <c r="D23" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="19" t="s">
+        <v>497</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>455</v>
+      </c>
+      <c r="C24" s="22">
+        <v>1</v>
+      </c>
+      <c r="D24" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>456</v>
+      </c>
+      <c r="C25" s="22">
+        <v>1</v>
+      </c>
+      <c r="D25" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="19" t="s">
+        <v>499</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>457</v>
+      </c>
+      <c r="C26" s="22">
+        <v>1</v>
+      </c>
+      <c r="D26" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>461</v>
+      </c>
+      <c r="C27" s="22">
+        <v>1</v>
+      </c>
+      <c r="D27" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>471</v>
+      </c>
+      <c r="C28" s="22">
+        <v>1</v>
+      </c>
+      <c r="D28" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>472</v>
+      </c>
+      <c r="C29" s="22">
+        <v>1</v>
+      </c>
+      <c r="D29" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="19" t="s">
+        <v>503</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>447</v>
+      </c>
+      <c r="C30" s="22">
+        <v>0</v>
+      </c>
+      <c r="D30" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>466</v>
+      </c>
+      <c r="C31" s="22">
+        <v>0</v>
+      </c>
+      <c r="D31" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>467</v>
+      </c>
+      <c r="C32" s="22">
+        <v>0</v>
+      </c>
+      <c r="D32" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>468</v>
+      </c>
+      <c r="C33" s="22">
+        <v>0</v>
+      </c>
+      <c r="D33" s="22">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
